--- a/data/grammar-explanations-4lang.xlsx
+++ b/data/grammar-explanations-4lang.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K254"/>
+  <dimension ref="A1:K350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -14521,6 +14521,5484 @@
       </c>
       <c r="K254" s="2" t="inlineStr"/>
     </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>十七歲還是二十五歲？</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>與其 A…不如 B… B rather than A</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>與其 A，不如 B</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>比較兩個選擇，說明第二個比較好。「與其 A，不如 B」是「與其做 A，還不如做 B」的意思。</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Mejor B que A: 與其…不如</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>與其 A，不如 B = en vez de A, es mejor B. Se compara dos opciones y se recomienda la segunda.</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>與其 A…不如 B… B rather than A</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>Compares two options and says the second is better. 與其 A，不如 B means 'rather than A, it would be better to B'.</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>與其在家看電視，不如出去走走。
+En vez de ver televisión en casa, mejor salir a caminar.
+Rather than watching TV at home, it's better to go out for a walk.</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>十七歲還是二十五歲？</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>就 on the contrary</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>表示對比的「就」</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>別人的想法或情況是一樣的，但說話的人（或這個人）卻不同，這時可以用「就」表示對比，意思像「卻」「反倒」。</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Contraste con 就</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>就 puede marcar un contraste inesperado: «en cambio, sin embargo». Los demás piensan una cosa y esta persona piensa lo contrario.</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>就 on the contrary</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>When others think or do one thing but this person differs, 就 marks the contrast, much like 'whereas' or 'on the contrary'.</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>大家都說這部電影很無聊，他就覺得很有意思。
+Todos dicen que esta película es aburrida; él, en cambio, la encuentra interesante.
+Everyone says this movie is boring, but he finds it interesting.</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>十七歲還是二十五歲？</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>A Summary of the Various Usages of 就</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>「就」的用法總整理</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>「就」常見的用法有：一、很快、馬上（我馬上就到）；二、強調「正是」（這就是……）；三、只有（就我一個人）；四、前後連接（要是……就……）。</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Usos de 就 (resumen)</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Resumen de 就: (1) enseguida, pronto; (2) enfático, «precisamente»; (3) «solo», limita una cantidad; (4) condición y resultado (要是…就…).</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>A Summary of the Various Usages of 就</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>Main uses of 就: (1) soon, right away; (2) emphatic 'precisely'; (3) 'only'; (4) linking condition and result (要是…就…).</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>我馬上就到。
+Llego enseguida.
+I'll be there right away.
+這就是我要找的書。
+Este es justamente el libro que busco.
+This is exactly the book I'm looking for.</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>十七歲還是二十五歲？</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>別說 A，就是 B 也… never mind A, even B is the case…</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>別說 A，就是 B 也…</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>先說一件比較難的事（A）都不行，連比較容易的事（B）也不行。意思是「連 B 都……，更不用說 A」。</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Ni A, ni B: 別說…就是</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>別說 A，就是 B 也… = ni hablar de A; incluso B (el caso más fácil) también…. A es el caso más difícil y B el más fácil.</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>別說 A，就是 B 也… never mind A, even B is the case…</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>First name the harder thing (A), then say even the easier thing (B) isn't possible either: 'forget A, even B…'.</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>別說跑步，就是走路他也覺得累。
+Ni hablar de correr; hasta caminar lo cansa.
+Forget running, even walking tires him out.</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>十七歲還是二十五歲？</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>簡直 to put it simply and plainly, it seems as if</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>簡直</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>「簡直」用來誇張地描述，意思是「幾乎就是」「根本就像」，可以表示讚美，也可以表示抱怨。</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Prácticamente: 簡直</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>簡直 = es simplemente…, casi como si… Exagera para dar énfasis (admiración o queja).</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>簡直 to put it simply and plainly, it seems as if</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>簡直 exaggerates for emphasis: 'it's practically…', 'it's simply like…'. It can express admiration or complaint.</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>他的中文說得簡直跟台灣人一樣好。
+Habla chino tan bien que parece taiwanés.
+He speaks Chinese so well that he sounds just like a Taiwanese person.</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>十七歲還是二十五歲？</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>不至於 but the situation would not be so bad as to …</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>不至於</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>「不至於」表示事情不會嚴重到那個地步，用來否定一個太誇張的想法。</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>No llega a tanto: 不至於</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>不至於 = no llega al punto de…, no sería tan grave. Sirve para descartar una posibilidad exagerada.</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>不至於 but the situation would not be so bad as to …</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>不至於 says things won't go as far as that; it's used to rule out an exaggerated possibility.</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>只是小感冒，不至於住院吧。
+Es solo un resfriado leve, no creo que haya que hospitalizarlo.
+It's just a mild cold; he surely doesn't need to be hospitalized.</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>十七歲還是二十五歲？</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>往往 usually, tend to</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>往往</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>「往往」表示照過去的經驗，常常是這樣，有規律性。不能用在未來，也不能用在只發生一次的事。</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Por lo general: 往往</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>往往 = por lo general, suele (patrón habitual basado en la experiencia). No se usa para el futuro ni para hechos únicos.</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>往往 usually, tend to</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>往往 describes what usually happens based on experience. It isn't used for the future or for one-time events.</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>週末的捷運往往很擠。
+Los fines de semana el metro suele estar lleno.
+On weekends the metro is usually crowded.</t>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>十七歲還是二十五歲？</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Do Something Just for Fun V 著玩</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>V 著玩</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>「V 著玩」表示只是為了好玩去做，不是認真的。</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Por diversión: V 著玩</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>V 著玩 = hacer algo solo por diversión, sin tomarlo en serio.</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>Do Something Just for Fun V 著玩</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>V 著玩 means doing something just for fun, not seriously.</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>我只是畫著玩，畫得不好。
+Solo dibujo por diversión, no dibujo bien.
+I'm only drawing for fun; I'm not good at it.
+別當真，他是說著玩的。
+No lo tomes en serio, lo dijo en broma.
+Don't take it seriously, he was just joking.</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>眼睛、耳朵的饗宴</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>Verb Complement 成 successful(ly)</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>動詞＋成（成功）</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>「V＋成」表示事情做成了、成功了。否定用「V 不成」，表示沒辦法完成。</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Lograr algo: V 成</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>V + 成 = lograr hacer algo (resultado exitoso). Negación: V 不成 = no se logró.</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>Verb Complement 成 successful(ly)</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>V + 成 shows that something was achieved successfully. Its negative, V 不成, means it couldn't be done.</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>這筆生意終於談成了。
+Por fin se cerró este negocio.
+This deal was finally closed.
+下雨了，我們去不成了。
+Está lloviendo, ya no podemos ir.
+It's raining, so we can't go anymore.</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>眼睛、耳朵的饗宴</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>萬一 supposing, in the event of something negative</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>萬一</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>「萬一」用在可能性很小、但如果發生會很糟的事情，意思是「如果真的……」。</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Por si acaso: 萬一</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>萬一 = en caso de que (algo malo y poco probable), por si acaso.</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>萬一 supposing, in the event of something negative</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>萬一 introduces something unlikely but bad if it happened: 'in case…', 'what if…'.</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>帶把傘吧，萬一下雨怎麼辦？
+Lleva un paraguas, ¿y si llueve?
+Bring an umbrella. What if it rains?</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>眼睛、耳朵的饗宴</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>以為 to have wrongly thought that…</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>以為</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>「以為」是自己想的跟事實不一樣，後來才發現弄錯了。</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Creer erróneamente: 以為</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>以為 = creer (equivocadamente) que…; la realidad resultó ser distinta.</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>以為 to have wrongly thought that…</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>以為 means you thought something that turned out to be wrong.</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>我以為今天放假，原來要上班。
+Creí que hoy era feriado, pero resulta que hay que trabajar.
+I thought today was a day off, but it turns out I have to work.</t>
+        </is>
+      </c>
+      <c r="K265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>眼睛、耳朵的饗宴</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Adverb 可</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>副詞「可」</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>「可」放在動詞或形容詞前面加強語氣，常用在提醒、警告或感嘆，是口語的說法。</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>El adverbio 可</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>可 como adverbio da énfasis: «sí que», «de verdad». Se usa en advertencias, exclamaciones y lenguaje coloquial.</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>Adverb 可</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>The adverb 可 adds emphasis before a verb or adjective, often in reminders, warnings or exclamations. It's colloquial.</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>你可別忘了明天的會議！
+¡No te vayas a olvidar de la reunión de mañana!
+Don't you forget about tomorrow's meeting!
+這家的牛肉麵可好吃了！
+¡Los fideos con carne de este lugar sí que están ricos!
+The beef noodles here are really delicious!</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>眼睛、耳朵的饗宴</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>免得 lest, so as to avoid</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>免得</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>「免得」放在後面的句子，表示為了避免不好的結果，所以前面先做某件事。</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Para evitar que: 免得</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>免得 = para evitar que, no sea que. Introduce la consecuencia no deseada y va en la segunda cláusula.</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>免得 lest, so as to avoid</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>免得 goes in the second clause: you do something first so as to avoid an unwanted result.</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>你先打電話問一下，免得白跑一趟。
+Llama antes a preguntar, para no ir en balde.
+Call and ask first, so you don't make a trip for nothing.</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>眼睛、耳朵的饗宴</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>曾經 experience in the past, V’ed before</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>曾經</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>「曾經」表示過去有過某種經驗，現在已經不是這樣了，常常跟「過」一起用。</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Alguna vez: 曾經</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>曾經 + V = alguna vez, en el pasado (una experiencia que ya no continúa). Suele ir con 過.</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>曾經 experience in the past, V’ed before</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>曾經 shows that something happened in the past and no longer holds now. It often appears with 過.</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>我曾經在台南住過一年。
+Una vez viví un año en Tainan.
+I once lived in Tainan for a year.</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>眼睛、耳朵的饗宴</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Enumeration Particle 等 etc…</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>列舉的「等」</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>列舉幾個例子後加上「等」，表示還有其他沒說完的，也可以說「等等」。</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Etcétera: 等</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>等 al final de una lista = etcétera; indica que hay más ejemplos. También se dice 等等.</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>Enumeration Particle 等 etc…</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>Add 等 after a list of examples to show there are more; 等等 also works.</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>夜市有臭豆腐、蚵仔煎、珍珠奶茶等小吃。
+En el mercado nocturno hay tofu apestoso, tortilla de ostras, té con perlas, etc.
+The night market has stinky tofu, oyster omelet, bubble tea and other snacks.</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>眼睛、耳朵的饗宴</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Making a Verb with the Particle 所</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>「所」＋動詞</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>「所」加在動詞前面，可以把一個動作變成名詞性的說法，意思是「……的（事／東西）」，比較書面。</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Lo que…: 所 + verbo</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>所 + verbo forma una expresión nominal de estilo formal: «lo que…». Ejemplos: 我所知道的, 他所說的.</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>Making a Verb with the Particle 所</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>所 before a verb turns it into a noun-like phrase meaning 'what…' or 'that which…'. It's fairly formal.</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>這就是我所知道的一切。
+Esto es todo lo que sé.
+This is everything I know.
+他所說的我都同意。
+Estoy de acuerdo con todo lo que dijo.
+I agree with everything he said.</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>雲端科技</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>何必 why must</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>何必</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>「何必」是反問，意思是「不需要」「沒有必要」，常用來勸人不要這樣做。</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>¿Para qué? 何必</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>何必 = ¿para qué…?, ¿por qué habrías de…? Es una pregunta retórica: no hace falta.</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>何必 why must</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>何必 is a rhetorical question meaning 'there's no need to…', often used to persuade someone not to do something.</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>只是小事，你何必這麼生氣？
+Es solo una tontería, ¿para qué enojarte tanto?
+It's only a small matter. Why get so angry?</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>雲端科技</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>不見得 not necessarily</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>不見得</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>「不見得」表示不一定，不一定是你想的那樣，語氣比較委婉。</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>No necesariamente: 不見得</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>不見得 = no necesariamente. Niega de forma suave que algo sea siempre así.</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>不見得 not necessarily</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>不見得 means 'not necessarily'. It's a mild way to say it isn't always as you think.</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>貴的東西不見得比較好。
+Lo caro no necesariamente es mejor.
+Expensive things are not necessarily better.</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>雲端科技</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>嘛 isn’t it obvious that</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>語氣詞「嘛」</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>「嘛」放在句尾，表示這件事很明顯、很簡單，或帶一點勸說、不耐煩的語氣，是口語的說法。</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>La partícula 嘛</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>嘛 al final de la oración es una partícula coloquial: indica que algo es obvio o insiste con un tono de reproche suave.</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>嘛 isn’t it obvious that</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>嘛 at the end of a sentence shows that something is obvious, or adds a gently persuasive or impatient tone. It's colloquial.</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>這很簡單嘛，你一定會的。
+Esto es fácil, ¿no ves?; seguro que puedes.
+It's easy, you know. I'm sure you can do it.
+有問題就問嘛。
+Si tienes dudas, pregunta, ¿no?
+If you have a question, just ask!</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>雲端科技</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Verb Particle 慣</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>動詞＋慣</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>「V＋慣」表示習慣了，例如「吃慣」「住慣」「用慣」。否定的「看不慣」是「看了不舒服、無法接受」。</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Acostumbrarse: V 慣</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>V + 慣 = estar acostumbrado a: 吃慣, 住慣, 用慣. En negativo, 看不慣 = no soportar ver algo.</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>Verb Particle 慣</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>V + 慣 means being used to something (吃慣, 住慣, 用慣). 看不慣 means you can't stand seeing it.</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>我已經吃慣台灣菜了。
+Ya me acostumbré a la comida taiwanesa.
+I'm already used to Taiwanese food.
+他看不慣別人亂丟垃圾。
+No soporta ver que otros tiren basura por cualquier lado.
+He can't stand seeing people litter.</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>雲端科技</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Verb Complement 動 capable of causing movement</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>動詞＋得動／不動</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>「V＋得動／不動」表示有沒有力氣把一個動作做完，例如「搬不動」「走不動」「吃不動」。</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>No tener fuerzas: V 得動／不動</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>V + 得動 / 不動 = tener / no tener fuerza para mover o hacer algo: 搬不動, 走不動, 吃不動.</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>Verb Complement 動 capable of causing movement</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>V + 得動 / 不動 shows whether you have the strength to do something, like 搬不動, 走不動, 吃不動.</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>這個箱子太重了，我搬不動。
+Esta caja pesa demasiado, no puedo moverla.
+This box is too heavy; I can't move it.
+我今天累得走不動了。
+Hoy estoy tan cansado que ya no puedo caminar.
+I'm so tired today that I can't walk anymore.</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>雲端科技</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>無形中 without knowing it, and before you know it</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>無形中</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>「無形中」表示不知不覺、慢慢地發生，自己沒有特別注意到。</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Sin darse cuenta: 無形中</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>無形中 = sin darse cuenta, de forma imperceptible y poco a poco.</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>無形中 without knowing it, and before you know it</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>無形中 means something happens imperceptibly and gradually, without you noticing.</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>常常看台劇，無形中他的中文進步了。
+Como veía series taiwanesas a menudo, su chino mejoró sin que se diera cuenta.
+He watched Taiwanese dramas often, and his Chinese improved without him realizing it.</t>
+        </is>
+      </c>
+      <c r="K276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>雲端科技</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>此外 in addition, furthermore</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>此外</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>「此外」是書面的連接詞，意思是「除了這個以外，還有……」，用來再加一點。</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>Además: 此外</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>此外 = además, aparte de esto. Es un conector de estilo formal que añade otro punto.</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>此外 in addition, furthermore</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>此外 is a formal connector meaning 'besides this, there is also…'; it adds another point.</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
+        <is>
+          <t>這家店的東西很新鮮，此外服務也很好。
+Los productos de esta tienda son muy frescos y, además, el servicio es muy bueno.
+The food at this shop is very fresh, and the service is great too.</t>
+        </is>
+      </c>
+      <c r="K277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>雲端科技</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>總而言之 in short</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>總而言之</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>「總而言之」用在說完幾個看法之後，引出簡短的結論。</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>En resumen: 總而言之</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>總而言之 = en resumen, en una palabra. Introduce la conclusión.</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>總而言之 in short</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>總而言之 introduces a brief conclusion after several points have been made.</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>總而言之，這個方法比較省時間。
+En resumen, este método ahorra más tiempo.
+In short, this method saves more time.</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>床該擺哪裡？</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>總算 finally, speaking roughly (in the ball park)</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>總算</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>「總算」表示等了很久或努力很久之後，終於有了結果，帶著鬆了一口氣的感覺。</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>Por fin: 總算</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>總算 = por fin, finalmente. Expresa alivio después de esperar o esforzarse mucho.</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>總算 finally, speaking roughly (in the ball park)</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>總算 shows that after a long wait or effort, a result finally came, with a sense of relief.</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
+        <is>
+          <t>等了三個月，簽證總算下來了。
+Después de esperar tres meses, por fin salió la visa.
+After waiting three months, the visa has finally come through.</t>
+        </is>
+      </c>
+      <c r="K279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>床該擺哪裡？</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>還不就是 nothing more than</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>還不就是</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>「還不就是」用來說「也不過是……」，把事情說得不重要，是口語的反問。</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>No es más que…: 還不就是</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>還不就是 = no es más que…, al fin y al cabo es solo… Resta importancia; tono coloquial.</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>還不就是 nothing more than</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>還不就是 is a colloquial rhetorical phrase meaning 'it's nothing more than…', playing down how important something is.</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>他們說的新方法，還不就是以前那一套？
+Ese «método nuevo» que dicen, ¿no es lo mismo de antes?
+That 'new method' they talk about is just the same old routine, isn't it?</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>床該擺哪裡？</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>Outright Denial with 才</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>表示強烈否定的「才」</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>「才不」「才沒有」用來強烈反駁，意思是「才不是這樣」「我才不要」。</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Negación fuerte con 才</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>才 enfático con negación: «eso sí que no», «claro que no». Contradice con fuerza lo que se dijo: 才不, 才沒有.</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>Outright Denial with 才</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>才不 / 才沒有 strongly denies or pushes back: 'no way', 'certainly not'.</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>我才不要去！
+¡Yo no pienso ir!
+I'm not going, no way!
+誰說我生氣了？我才沒有。
+¿Quién dijo que estoy enojado? Para nada.
+Who said I was angry? I'm not.</t>
+        </is>
+      </c>
+      <c r="K281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>床該擺哪裡？</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>A Summary of the Various Usages of 才</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>「才」的用法總整理</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>「才」常見的用法有：一、做完某件事之後才能……；二、數量很少（才八點）；三、比預期晚（十點才來）；四、強烈否定（我才不去）。</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Usos de 才 (resumen)</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>Resumen de 才: (1) «solo entonces» (condición previa); (2) «apenas» (cantidad pequeña); (3) más tarde de lo esperado; (4) negación enfática (我才不去).</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>A Summary of the Various Usages of 才</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>Main uses of 才: (1) only after something is done; (2) 'only/just' for small amounts; (3) later than expected; (4) emphatic denial.</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>你先寫完功課才可以玩。
+Solo después de terminar la tarea puedes jugar.
+You can only play after you finish your homework.
+他昨天十二點才睡。
+Ayer no se durmió hasta las doce.
+He didn't go to sleep until twelve yesterday.</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>床該擺哪裡？</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>所謂（的） A 是指 B so called A refers to B</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>所謂（的）A，是指 B</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>用來解釋一個詞的意思：「所謂 A」就是「大家說的 A」，後面接「是指 B」說明它是什麼。</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>Definir: 所謂…是指</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>所謂（的）A，是指 B = lo que se llama A se refiere a B. Sirve para definir un término.</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>所謂（的） A 是指 B so called A refers to B</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>Used to define a term: 所謂 A means 'what is called A', followed by 是指 B to say what it refers to.</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
+        <is>
+          <t>所謂「宵夜」，是指晚餐以後吃的東西。
+Lo que se llama «xiaoye» se refiere a lo que se come después de la cena.
+'Xiaoye' refers to what you eat after dinner.</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>床該擺哪裡？</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>一口氣 lit. in one breath</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>一口氣</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>「一口氣」表示一次就做完，中間不停，不休息。</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>De un tirón: 一口氣</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>一口氣 = de un tirón, sin parar (en una sola respiración).</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>一口氣 lit. in one breath</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>一口氣 means doing something in one go, without stopping or resting.</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>他一口氣喝完了一大杯水。
+Se tomó de un trago un vaso grande de agua.
+He drank a large glass of water in one gulp.
+我一口氣把書看完了。
+Me leí el libro de un tirón.
+I read the whole book in one go.</t>
+        </is>
+      </c>
+      <c r="K284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>床該擺哪裡？</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>光 A 就… just A alone…</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>光 A 就…</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>「光 A 就……」表示只算 A 這一項，就已經很多了，更不用算別的。</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>Solo A ya…: 光 A 就</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>光 A 就… = solo A ya… Solo eso ya es mucho, sin contar lo demás.</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>光 A 就… just A alone…</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>光 A 就… means that A alone is already a lot, without counting anything else.</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr">
+        <is>
+          <t>光機票就要三萬塊。
+Solo el pasaje de avión ya cuesta treinta mil dólares.
+The plane ticket alone costs thirty thousand dollars.</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>床該擺哪裡？</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Expressing Displeasure or Annoyance with 都</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>表示抱怨的「都」</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>「都是你……」表示責怪，說因為你才會這樣；「都＋時間＋了」表示已經這麼晚了，還沒做某件事。</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>Queja con 都</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>都 + causa o tiempo expresa queja o fastidio: 都是你… = es todo culpa tuya; 都 + hora + 了 = ya es tan tarde y todavía….</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>Expressing Displeasure or Annoyance with 都</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>都是你… blames someone ('it's all your fault'); 都 + time + 了 means 'it's already this late, and yet…'.</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
+        <is>
+          <t>都是你，我們才會遲到！
+¡Por tu culpa llegamos tarde!
+It's all your fault that we're late!
+都十二點了，你還不睡？
+Ya son las doce, ¿todavía no te duermes?
+It's already twelve o'clock; aren't you going to sleep yet?</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>有夢最美</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>Rhetorical Question with 哪裡</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>反問的「哪裡」</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>「哪裡」放在動詞或形容詞前面，用反問的方式表示否定，意思是「怎麼會」「才不是」。回答別人稱讚時說「哪裡哪裡」，是謙虛的說法。</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>Pregunta retórica: 哪裡</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>哪裡 + verbo / adjetivo = negación retórica: «qué va», «cómo voy a…». También se usa como respuesta modesta a un halago.</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>Rhetorical Question with 哪裡</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>哪裡 before a verb or adjective makes a rhetorical negation: 'how could…', 'not at all'. Replying 哪裡 to a compliment is a modest answer.</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
+        <is>
+          <t>我哪裡知道他今天不來？
+¿Cómo iba a saber yo que hoy no venía?
+How would I know he isn't coming today?
+哪裡，我的中文還不夠好。
+Qué va, mi chino todavía no es suficientemente bueno.
+Not at all, my Chinese still isn't good enough.</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>有夢最美</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>畢竟 after all</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>畢竟</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>「畢竟」提醒對方最根本的原因，意思是「說到底」「終究」。</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>Al fin y al cabo: 畢竟</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>畢竟 = al fin y al cabo, después de todo. Recuerda la razón de fondo.</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>畢竟 after all</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>畢竟 points to the underlying reason: 'after all', 'when all is said and done'.</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>他畢竟還是個孩子，別太嚴格。
+Al fin y al cabo es un niño, no seas tan estricto.
+After all, he's still a child, so don't be too strict.</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>有夢最美</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>的確 indeed</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>的確</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>「的確」用來確認一件事是真的，意思是「確實」。</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>Efectivamente: 的確</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>的確 = efectivamente, realmente. Confirma que algo es cierto.</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>的確 indeed</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>的確 confirms that something is true: 'indeed', 'certainly'.</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>這家店的牛肉麵的確很好吃。
+Los fideos con carne de este lugar de verdad están muy ricos.
+The beef noodles at this shop really are delicious.</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>有夢最美</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>話說回來 however, on the other hand</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>話說回來</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>「話說回來」用來轉到另一個角度，或把話題拉回來，意思是「不過」「說回來」。</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>Por otro lado: 話說回來</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>話說回來 = pero, por otro lado; dicho esto. Introduce otro punto de vista o vuelve al tema.</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>話說回來 however, on the other hand</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>話說回來 shifts to another angle or brings the topic back: 'that said', 'on the other hand'.</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>台北交通很方便，話說回來，房租也真的很貴。
+En Taipéi el transporte es muy cómodo, pero, por otro lado, la renta sí que es cara.
+Transportation in Taipei is very convenient, but then again, the rent is really expensive.</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>有夢最美</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>NP 之所以 S2 是因為 S1 S2 is due to S1</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>NP 之所以 S2，是因為 S1</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>先說結果，再說原因：「之所以……，是因為……」。比「因為……所以……」更強調原因。</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>La razón es…: 之所以…是因為</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>NP 之所以 S2，是因為 S1 = la razón por la que S2 es que S1. Primero se dice el resultado y luego la causa.</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>NP 之所以 S2 是因為 S1 S2 is due to S1</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>State the result first, then the cause: 之所以…，是因為…. It puts more weight on the reason than 因為…所以….</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>他之所以能考上，是因為他每天都很努力。
+La razón por la que pudo entrar es que se esforzaba todos los días.
+The reason he got in is that he worked hard every day.</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>有夢最美</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>根本 not…at all</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>根本</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>「根本」放在否定的句子裡，表示完全不是這樣，意思是「從來就不」「完全不」。</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>En absoluto: 根本</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>根本 + negación = en absoluto, de ninguna manera. Enfatiza que no es así desde el fondo.</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>根本 not…at all</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>根本 in a negative sentence means 'not at all', 'not even in the slightest'.</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>我根本不知道這件事。
+No tenía ni idea de este asunto.
+I had no idea about this matter at all.</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>有夢最美</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>更別說…了 let alone, never mind</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>更別說…了</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>先說一件比較容易的事都做不到，再說「更別說 A 了」，表示更難的事當然做不到。</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>Y mucho menos: 更別說…了</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>更別說 A 了 = y mucho menos A, ni hablar de A. Se niega un caso más difícil después de uno más fácil.</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>更別說…了 let alone, never mind</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>After saying someone can't even do the easier thing, 更別說 A 了 adds that the harder thing is out of the question.</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>他連中文都不會說，更別說寫了。
+Ni siquiera sabe hablar chino, y mucho menos escribirlo.
+He can't even speak Chinese, let alone write it.</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>有夢最美</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>恨不得 one really wishes one could…</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>恨不得</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>「恨不得」表示非常想做某件事，但通常做不到。</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>Desear con fuerza: 恨不得</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>恨不得 + verbo = desear con todas las fuerzas poder hacer algo (a menudo imposible).</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>恨不得 one really wishes one could…</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>恨不得 means desperately wanting to do something, usually something you can't actually do.</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>太累了，我恨不得馬上就能睡覺。
+Estoy tan cansado que quisiera poder dormirme ya mismo.
+I'm so tired I wish I could fall asleep right now.
+聽到好消息，他恨不得馬上告訴大家。
+Al oír la buena noticia, se moría por contárselo a todos.
+Hearing the good news, he couldn't wait to tell everyone.</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>天搖地動</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>怎麼這麼 Why so…?</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>怎麼這麼</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>「怎麼這麼＋形容詞／動詞」表示驚訝或抱怨，意思是「為什麼這麼……」。</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>¿Por qué tan…? 怎麼這麼</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>怎麼這麼 + adjetivo / verbo = ¿por qué tan…? Expresa sorpresa o queja.</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>怎麼這麼 Why so…?</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>怎麼這麼 + adjective / verb expresses surprise or complaint: 'why so…?'.</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>今天怎麼這麼冷？
+¿Por qué hace tanto frío hoy?
+Why is it so cold today?</t>
+        </is>
+      </c>
+      <c r="K295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>天搖地動</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Intensifying Adverb 多 how</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>感嘆的「多」</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>「多＋形容詞」用在感嘆句，意思是「多麼……」，句尾常加「啊」「呀」。</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Exclamación con 多</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>多 + adjetivo en una exclamación = ¡qué…! Suele cerrar con 啊 / 呀 y expresa admiración.</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>Intensifying Adverb 多 how</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>多 + adjective in an exclamation means 'how…!', and often ends with 啊 or 呀.</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>這裡的風景多美啊！
+¡Qué hermoso es el paisaje de aquí!
+How beautiful the scenery is here!</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>天搖地動</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>The Various Functions of 多</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>「多」的各種用法</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>「多」常見的用法有：一、數字後面表示「超過」（三十多歲）；二、問程度（多高）；三、感嘆（多好看）；四、「不管多……」表示「再……也」。</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>Usos de 多 (resumen)</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>Funciones de 多: (1) «más de» después de un número; (2) pregunta de grado (多高, 多久); (3) exclamación «qué…»; (4) «por más… que» en 不管多….</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>The Various Functions of 多</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>Common uses of 多: (1) 'more than' after a number; (2) asking degree (多高); (3) exclamation 'how…'; (4) 不管多… for 'no matter how…'.</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>他今年三十多歲。
+Este año tiene treinta y tantos.
+He's in his thirties this year.
+不管多忙，我都會陪家人吃晚飯。
+Por muy ocupado que esté, ceno con mi familia.
+No matter how busy I am, I eat dinner with my family.</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>天搖地動</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>白 in vain, for nothing</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>「白＋動詞」表示做了卻沒有結果、沒有用，例如「白跑一趟」。也可以表示「不用付錢」（白吃）。</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>En vano: 白</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>白 + verbo = en vano, para nada, sin resultado: 白跑一趟 = ir en balde. También puede significar «gratis» (白吃).</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>白 in vain, for nothing</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>白 + verb means doing something with no result, such as 白跑一趟 (a wasted trip). It can also mean 'for free' (白吃).</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>我白等了一個小時。
+Esperé una hora en vano.
+I waited an hour for nothing.
+他白跑了一趟。
+Fue en balde.
+He made a trip for nothing.</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>天搖地動</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>總是 always</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>總是</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>「總是」表示一直都是這樣，是固定的習慣，有時帶一點抱怨。</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>Siempre: 總是</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>總是 = siempre, constantemente. Es un hábito constante, a veces con un tono de queja.</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>總是 always</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>總是 means 'always', a constant habit, sometimes with a slight tone of complaint.</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>他總是遲到。
+Siempre llega tarde.
+He's always late.</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>天搖地動</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>The Various Meanings of the Verb Complement 下來</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>動詞＋下來</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>「V＋下來」常見的意思有：一、從上往下；二、把東西記錄或留住（記下來、留下來）；三、從過去持續到現在；四、變安靜、變穩定（安靜下來）。</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>V 下來 (resumen)</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>V + 下來: (1) de arriba hacia abajo; (2) algo queda registrado o se queda (記下來, 留下來); (3) continuar hasta ahora; (4) calmarse (安靜下來).</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>The Various Meanings of the Verb Complement 下來</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>Common meanings of V + 下來: (1) downward; (2) recording or keeping something (記下來, 留下來); (3) lasting up to now; (4) calming down.</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>請把這個電話號碼記下來。
+Por favor anota este número de teléfono.
+Please write down this phone number.
+聽到音樂，他慢慢安靜下來了。
+Al oír la música, poco a poco se fue calmando.
+Hearing the music, he gradually calmed down.</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>天搖地動</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>當…的時候 when, while, at the time of</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>當…的時候</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>「當＋一段話＋的時候」表示「在……的時間」，比只說「……的時候」稍微正式一點。</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>Cuando: 當…的時候</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>當 + frase + 的時候 = cuando, mientras, en el momento en que…. 當 hace la expresión un poco más formal.</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>當…的時候 when, while, at the time of</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>當 + clause + 的時候 means 'at the time when…'; it's slightly more formal than just …的時候.</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>當我到家的時候，天已經黑了。
+Cuando llegué a casa, ya había oscurecido.
+When I got home, it was already dark.</t>
+        </is>
+      </c>
+      <c r="K301" s="2" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>天搖地動</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>反而 on the contrary</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>反而</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>「反而」表示結果和預期相反，意思是「結果卻是」。</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Al contrario: 反而</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>反而 = al contrario, en cambio. El resultado va en contra de lo esperado.</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>反而 on the contrary</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>反而 shows that the result is the opposite of what you'd expect: 'on the contrary', 'instead'.</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>吃了藥，他不但沒好，反而更不舒服了。
+Tomó la medicina y no solo no mejoró, sino que se sintió peor.
+He took the medicine, and not only didn't he get better, he felt even worse.
+我已經提醒他了，他反而生氣了。
+Ya se lo recordé y, al contrario, se enojó.
+I already reminded him, and he got angry instead.</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>大學生的事</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>還 to my surprise</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>表示意外的「還」</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>「還」可以表示事情比想像的更好、更多，帶有一點意外。常見的說法有「還會……」「還有……」。</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>Sorpresa con 還</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>還 expresa sorpresa: algo resulta mejor o más de lo esperado. Suele aparecer en frases como 還會…, 還有….</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>還 to my surprise</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>還 expresses surprise that something is better or more than expected. Common patterns are 還會… and 還有….</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>這麼難的歌，他還會唱！
+¡Hasta sabe cantar una canción tan difícil!
+He can even sing such a hard song!
+沒想到這家店還有賣中文書。
+No esperaba que esta tienda hasta vendiera libros en chino.
+I didn't expect this shop to sell Chinese books, too.</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>大學生的事</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Alternating Events with 一下…一下…</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>一下……一下……</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>「一下 A，一下 B」表示兩種情況很快輪流出現，一下子這樣、一下子那樣。</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>Alternar: 一下…一下…</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>一下 A，一下 B = ahora A, ahora B. Describe dos situaciones que se alternan rápidamente.</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>Alternating Events with 一下…一下…</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>一下 A, 一下 B means 'one moment A, the next moment B'. Two situations alternate quickly.</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>他一下高興、一下難過，真讓人搞不懂。
+Un rato está contento y otro triste; es difícil entenderlo.
+He's happy one moment and sad the next; it's hard to figure him out.
+天氣一下熱、一下冷，很容易感冒。
+El clima cambia de calor a frío todo el tiempo; es fácil resfriarse.
+The weather swings between hot and cold; it's easy to catch a cold.</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>大學生的事</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>Various Fractions with A 分之 B</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>分數：A 分之 B</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>說分數時，先說分母（A），再說分子（B），中間加「分之」。百分比用「百分之」。</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>Fracciones: A 分之 B</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>A 分之 B expresa fracciones: se dice primero el denominador (A) y luego el numerador (B). Los porcentajes usan 百分之.</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>Various Fractions with A 分之 B</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>For fractions, say the denominator (A) first, then 分之, then the numerator (B). Percentages use 百分之.</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>全班有三分之一的人去過日本。
+Un tercio de la clase ha ido a Japón.
+A third of the class has been to Japan.
+這家公司百分之八十的員工是女生。
+El ochenta por ciento de los empleados de esta empresa son mujeres.
+Eighty percent of the employees at this company are women.</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>大學生的事</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>一連 without interruption, in rapid succession</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>一連</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>「一連＋數量＋動詞」表示動作連續發生好幾次，或持續好幾天，中間沒有停。</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Seguidos: 一連</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>一連 + cantidad + verbo = varias veces o durante varios días seguidos, sin interrupción.</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>一連 without interruption, in rapid succession</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>一連 + quantity + verb means an action happens several times or for several days in a row, without a break.</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>他一連請了三天假。
+Pidió permiso tres días seguidos.
+He took leave for three days in a row.
+這個星期一連下了五天雨。
+Esta semana llovió cinco días seguidos.
+It rained for five days straight this week.</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>大學生的事</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>To Have a Full Dosage of an Activity V 個夠</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>動詞＋個夠</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>「動詞＋個夠」表示盡情做某件事，做到滿意為止，例如「玩個夠」「吃個夠」「睡個夠」。</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>Hasta saciarse: V 個夠</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>Verbo + 個夠 = hacer algo hasta quedar satisfecho, a más no poder (玩個夠, 吃個夠, 睡個夠).</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>To Have a Full Dosage of an Activity V 個夠</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>Verb + 個夠 means doing something to your heart's content, as in 玩個夠, 吃個夠, 睡個夠.</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>放假的時候，我想睡個夠。
+En las vacaciones quiero dormir todo lo que quiera.
+On vacation I want to sleep as much as I like.
+今天我們一定要吃個夠！
+¡Hoy vamos a comer hasta hartarnos!
+Today we're definitely going to eat our fill!</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>大學生的事</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>有助於 be conducive to</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>有助於</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>「有助於」是「對……有幫助」的比較正式說法，後面接動詞或名詞。</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Ayudar a: 有助於</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>有助於 + verbo / sustantivo = ayudar a, ser útil para. Es una forma más formal de 對…有幫助.</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>有助於 be conducive to</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>有助於 + verb/noun means 'helps with / is conducive to'. It is a more formal way of saying 對…有幫助.</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>多聽多說有助於提高中文程度。
+Escuchar y hablar mucho ayuda a mejorar el nivel de chino.
+Listening and speaking a lot helps improve your Chinese.
+運動有助於睡眠。
+El ejercicio ayuda a dormir.
+Exercise helps you sleep.</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>大學生的事</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>於是… thus, consequently</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>於是</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>「於是」表示因為前面的事，接著發生了後面的事，意思是「所以就」。前後兩件事有先後順序。</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>Así que: 於是</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>於是 = así que, por eso (en consecuencia). Une dos hechos en orden: el segundo ocurre a causa del primero.</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>於是… thus, consequently</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>於是 means 'so / as a result'. The second event follows from the first, in order.</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr">
+        <is>
+          <t>他覺得中文很有趣，於是決定去台灣學。
+Le pareció que el chino era interesante, así que decidió ir a estudiarlo a Taiwán.
+He found Chinese interesting, so he decided to study it in Taiwan.
+外面下大雨，於是我們留在家裡看電影。
+Llovía a cántaros afuera, así que nos quedamos en casa viendo una película.
+It was pouring outside, so we stayed home and watched a movie.</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>大學生的事</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>向 to, toward</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>介詞「向」</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>「向」後面接人或方向，表示動作的對象或方向，例如「向……借」「向……道謝」「向前走」。</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Hacia, a: 向</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>向 + persona o dirección = hacia, a, de. Marca el destinatario de una acción: 向…借, 向…道謝, 向前走.</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>向 to, toward</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>向 + person or direction marks the target or direction of an action, as in 向…借, 向…道謝, 向前走.</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>我想向你借一本書。
+Quiero pedirte prestado un libro.
+I'd like to borrow a book from you.
+他向大家說明了新的規定。
+Les explicó a todos las nuevas reglas.
+He explained the new rules to everyone.</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>他們的選擇</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>反正 at any rate, anyway</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>反正</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>「反正」表示不管怎麼樣，結果都一樣，所以不用在意或不必再討論。</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>De todos modos: 反正</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>反正 = de todos modos, total. Se usa cuando la situación no cambia, haga lo que se haga.</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>反正 at any rate, anyway</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>反正 means 'anyway': whatever happens, the result is the same, so there's no need to worry or argue about it.</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr">
+        <is>
+          <t>你不用擔心，反正我們時間很多。
+No te preocupes, total tenemos mucho tiempo.
+Don't worry, we have plenty of time anyway.
+反正我已經決定了，你說什麼都沒用。
+De todos modos ya decidí; nada de lo que digas servirá.
+I've already decided anyway; nothing you say will help.</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>他們的選擇</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>不只 not merely, exceeding</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>不只……還／也……</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>「不只 A，還／也 B」表示除了 A 以外，B 也是，範圍比 A 更大。</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>No solo: 不只</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>不只 A，還／也 B = no solo A, sino también B. La parte B añade algo más.</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>不只 not merely, exceeding</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>不只 A, 還/也 B means 'not only A, but also B'; B adds something beyond A.</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr">
+        <is>
+          <t>他不只會說中文，還會說日文。
+No solo habla chino, también habla japonés.
+He doesn't just speak Chinese; he speaks Japanese, too.
+不只小孩喜歡這部電影，大人也很喜歡。
+No solo a los niños les gusta esta película; a los adultos también.
+It's not only kids who like this movie; adults like it, too.</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>他們的選擇</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>難免 inevitably, it is only natural that</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>難免</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>「難免」表示在這種情況下，很容易發生某件事，幾乎無法避免。</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Inevitable: 難免</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>難免 = es inevitable, es natural que. Se usa para algo que casi siempre pasa en esa situación.</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>難免 inevitably, it is only natural that</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>難免 means 'it's hard to avoid / it's only natural': something is very likely to happen in this situation.</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>剛開始學中文，難免會說錯。
+Al empezar a aprender chino es inevitable equivocarse al hablar.
+When you first start learning Chinese, it's inevitable that you'll make mistakes.
+第一次出國，難免會有點緊張。
+La primera vez que se viaja al extranjero es normal estar un poco nervioso.
+Going abroad for the first time, it's natural to feel a bit nervous.</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>他們的選擇</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>倒是 on the other hand</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>倒是</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>「倒是」表示和前面說的有一點相反或不同，語氣比較輕，意思是「不過……卻……」。</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Eso sí: 倒是</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>倒是 = en cambio, eso sí. Introduce un contraste suave con lo anterior.</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>倒是 on the other hand</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>倒是 introduces a mild contrast with what came before: 'but, on the other hand'.</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>這家餐廳不大，東西倒是挺好吃的。
+Este restaurante no es grande, pero la comida sí que es bastante rica.
+This restaurant isn't big, but the food is actually quite good.
+他中文說得不太好，字倒是寫得很漂亮。
+No habla muy bien chino, pero eso sí, escribe los caracteres muy bonito.
+His Chinese isn't great, but his handwriting is really beautiful.</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>他們的選擇</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>這下子 that being the case, as a consequence</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>這下子</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>「這下子」表示因為剛才發生的事，產生了新的結果，可以是好事，也可以是壞事。</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Ahora sí: 這下子</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>這下子 = ahora sí, con esto. Señala la consecuencia de lo que acaba de ocurrir (buena o mala).</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>這下子 that being the case, as a consequence</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>這下子 means 'now, with this': it points to the consequence of what just happened, good or bad.</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr">
+        <is>
+          <t>鑰匙不見了，這下子麻煩了！
+Se perdieron las llaves, ¡ahora sí estamos en problemas!
+The keys are lost, so now we're in trouble!
+他考上了，這下子爸媽可以放心了。
+Aprobó el examen; ahora sí sus papás pueden estar tranquilos.
+He got in, so now his parents can relax.</t>
+        </is>
+      </c>
+      <c r="K315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>他們的選擇</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>Verb Complement 來 personable</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>動詞＋得來／不來</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>「動詞＋得來／不來」表示跟某人或某件事合不合得上，例如「合得來」「談得來」「合不來」。</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Congeniar: V 得來／不來</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>Verbo + 得來 / 不來 expresa si algo se lleva bien con uno: 合得來 (llevarse bien), 談得來 (conectar al conversar), 合不來 (no congeniar).</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>Verb Complement 來 personable</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>Verb + 得來/不來 says whether you get along with someone or something suits you, as in 合得來, 談得來, 合不來.</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr">
+        <is>
+          <t>我跟新室友很談得來。
+Con mi nuevo compañero de cuarto conecto muy bien al conversar.
+I really click with my new roommate when we talk.
+他們兩個個性不同，合不來。
+Esos dos tienen personalidades distintas y no congenian.
+The two of them have different personalities and don't get along.</t>
+        </is>
+      </c>
+      <c r="K316" s="2" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>他們的選擇</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>何況 let alone, no need to mention</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>何況</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>「何況」用更明顯的例子來加強前面的說法，意思是「更不用說」「而且」。</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>Cuánto más: 何況</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>何況 = y más aún, cuánto más. Para reforzar un argumento con un caso aún más claro.</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>何況 let alone, no need to mention</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>何況 strengthens an argument with an even clearer case: 'let alone', 'not to mention'.</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr">
+        <is>
+          <t>連大人都搬不動，何況是小孩？
+Ni los adultos pueden moverlo, ¿cuánto menos un niño?
+Even adults can't move it, let alone a child.
+這麼近，何況天氣又好，我們走路去吧。
+Está tan cerca y además hace buen tiempo; vayamos caminando.
+It's so close, and the weather is nice, too, so let's walk.</t>
+        </is>
+      </c>
+      <c r="K317" s="2" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>他們的選擇</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>否則 otherwise</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>否則</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>「否則」表示如果前面說的事沒有做到，就會有不好的結果，意思是「不然」。</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>De lo contrario: 否則</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>否則 = de lo contrario, si no. Introduce lo que pasará si no se cumple lo anterior.</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>否則 otherwise</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>否則 means 'otherwise': if the previous condition isn't met, something bad will happen.</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr">
+        <is>
+          <t>快一點，否則會趕不上火車。
+Date prisa; si no, perderemos el tren.
+Hurry up, or we'll miss the train.
+你要多休息，否則身體會受不了。
+Tienes que descansar más; de lo contrario, tu cuerpo no lo resistirá.
+You need to rest more; otherwise your body won't be able to take it.</t>
+        </is>
+      </c>
+      <c r="K318" s="2" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>4-9</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>再談台灣故事</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>把 A 當做 B to treat, take A as B</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>把 A 當做 B</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>「把 A 當做 B」表示把 A 看成 B，或用對待 B 的方式對待 A。</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>Considerar: 把A當做B</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>把 A 當做 B = tratar o considerar a A como B.</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>把 A 當做 B to treat, take A as B</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>把 A 當做 B means to treat or regard A as B.</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr">
+        <is>
+          <t>我把他當做自己的弟弟。
+Lo considero como a mi propio hermano menor.
+I think of him as my own younger brother.
+很多人把網路當做主要的資訊來源。
+Mucha gente considera internet su principal fuente de información.
+Many people regard the internet as their main source of information.</t>
+        </is>
+      </c>
+      <c r="K319" s="2" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>4-9</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>再談台灣故事</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>在…下 under the…, due to the…</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>在……下</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>「在……下」表示在某種條件、幫助或情況之下，例如「在……的幫助下」「在這種情況下」。</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Bajo, con: 在…下</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>在…下 = bajo, con (condición, ayuda o circunstancia): 在…的幫助下, 在這種情況下.</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>在…下 under the…, due to the…</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>在…下 means 'under / with' a condition, help or circumstance, as in 在…的幫助下 and 在這種情況下.</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>在朋友的幫助下，我找到了工作。
+Con la ayuda de un amigo, encontré trabajo.
+With a friend's help, I found a job.
+在這樣的天氣下，比賽還是照常舉行。
+Aun con este clima, el partido se celebra como de costumbre.
+Even in this weather, the game is going ahead as usual.</t>
+        </is>
+      </c>
+      <c r="K320" s="2" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>4-9</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>再談台灣故事</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>The Various Functions of 該</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>「該」的各種用法</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>「該」可以表示「應該」（我該走了）、「到了該做某事的時候」（該……了），書面語裡也可以指前面提過的人或事，意思是「這個、那個」（該公司）。</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>Usos de 該</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>該 tiene varios usos: «deber» (我該走了), «ya es hora de…» (該…了), y en lenguaje escrito «dicho, el mencionado» (該公司).</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>The Various Functions of 該</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>該 can mean 'should' (我該走了), 'it's time to…' (該…了), and in written language 'the said / that' (該公司).</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr">
+        <is>
+          <t>太晚了，我該回家了。
+Es muy tarde, ya debo irme a casa.
+It's too late; I should head home now.
+該公司成立於一九八〇年。
+Dicha empresa fue fundada en 1980.
+The said company was founded in 1980.</t>
+        </is>
+      </c>
+      <c r="K321" s="2" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>4-9</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>再談台灣故事</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>自從…以後 ever since...</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>自從……以後</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>「自從……以後」表示從某個時間開始，到現在一直是同樣的情況。</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Desde que: 自從…以後</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>自從 + tiempo + 以後 = desde que…; la situación empieza en ese momento y continúa hasta ahora.</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>自從…以後 ever since...</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>自從…以後 means 'ever since': a situation starts at some point and has continued until now.</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr">
+        <is>
+          <t>自從搬到台北以後，我就很少回老家了。
+Desde que me mudé a Taipéi, rara vez vuelvo a mi pueblo.
+Since I moved to Taipei, I rarely go back to my hometown.
+自從學了中文以後，他交了很多新朋友。
+Desde que estudió chino, ha hecho muchos amigos nuevos.
+Since he started studying Chinese, he has made a lot of new friends.</t>
+        </is>
+      </c>
+      <c r="K322" s="2" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>4-9</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>再談台灣故事</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>Summary of the Various Usages of 幾</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>「幾」的各種用法</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>「幾」可以問「多少」（你要幾個？）、表示不多的數量（幾天），放在數字後面表示零頭（十幾個），「好幾」表示相當多。</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>Usos de 幾</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>幾 pregunta «cuántos» (números pequeños), significa «unos cuantos» (幾天) y, tras un número, «y tantos» (十幾個). 好幾 = bastantes.</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>Summary of the Various Usages of 幾</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>幾 asks 'how many' (small numbers), means 'a few' (幾天), means 'and some' after a number (十幾個), and 好幾 means 'quite a lot'.</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr">
+        <is>
+          <t>你要買幾個？
+¿Cuántos quieres comprar?
+How many do you want to buy?
+我已經等了好幾個小時了。
+Ya llevo esperando bastantes horas.
+I've been waiting for quite a few hours already.</t>
+        </is>
+      </c>
+      <c r="K323" s="2" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>4-9</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>再談台灣故事</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>不禁 uncontrollably, cannot help but…</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>不禁</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>「不禁」表示忍不住做某個動作，是自然、不自覺的反應。</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>No poder evitar: 不禁</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>不禁 + verbo = no poder evitar hacer algo (una reacción involuntaria).</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>不禁 uncontrollably, cannot help but…</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>不禁 means 'can't help (doing something)': an involuntary, natural reaction.</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>聽到這個好消息，我不禁笑了出來。
+Al oír la buena noticia no pude evitar reírme.
+Hearing the good news, I couldn't help laughing.
+看到老朋友的照片，他不禁想起了以前的日子。
+Al ver la foto de un viejo amigo, no pudo evitar recordar los viejos tiempos.
+Seeing a photo of an old friend, he couldn't help remembering the old days.</t>
+        </is>
+      </c>
+      <c r="K324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>4-9</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>再談台灣故事</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>仍然 still the same, same as before</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>仍然</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>「仍然」表示經過一段時間或有了變化，情況還是和以前一樣。</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>Todavía: 仍然</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>仍然 = todavía, aun así. La situación no cambia a pesar del tiempo o de las circunstancias.</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>仍然 still the same, same as before</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>仍然 means 'still / even so': the situation stays the same despite time or circumstances.</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr">
+        <is>
+          <t>過了十年，他仍然住在同一個地方。
+Pasaron diez años y él sigue viviendo en el mismo lugar.
+Ten years have passed and he still lives in the same place.
+雖然很累，他仍然堅持把工作做完。
+Aunque estaba muy cansado, insistió en terminar el trabajo.
+Although he was tired, he still insisted on finishing the work.</t>
+        </is>
+      </c>
+      <c r="K325" s="2" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>4-9</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>再談台灣故事</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>究竟 I wonder</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>究竟</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>「究竟」用在疑問句裡，追問真正的答案，意思是「到底」，語氣比「到底」正式。</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>En realidad: 究竟</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>究竟 = en realidad, a fin de cuentas. Se usa en preguntas para insistir en la respuesta; es más formal que 到底.</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>究竟 I wonder</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>究竟 is used in questions to press for the real answer: 'on earth, exactly'. It's more formal than 到底.</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>你究竟想不想去？
+¿En realidad quieres ir o no?
+Do you actually want to go or not?
+這件事究竟是誰的錯？
+¿De quién es la culpa de esto, a fin de cuentas?
+Whose fault is this, in the end?</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>應徵</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>Summary of the Various Functions of 著</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>「著」的各種用法</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>「著」可以表示狀態持續（牆上掛著畫）、動作的方式（笑著說），也可以表示背景動作正在進行。</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Usos de 著</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>著 marca un estado que continúa (牆上掛著畫), la manera en que se hace una acción (笑著說) y también una acción de fondo que sigue en curso.</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>Summary of the Various Functions of 著</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>著 can mark a continuing state (牆上掛著畫), the manner of an action (笑著說), or an ongoing background action.</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>牆上掛著一幅畫。
+En la pared hay colgado un cuadro.
+There's a painting hanging on the wall.
+他笑著對我說：「謝謝！」
+Me dijo sonriendo: «¡Gracias!».
+He said to me with a smile, 'Thank you!'</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>應徵</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>The Various Meanings of 中</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>「中」的各種意思</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>「中」（ㄓㄨㄥ）表示在某個範圍或過程裡，例如「討論中」；讀成ㄓㄨㄥˋ時是「打中、得到」的意思，例如「中獎」。</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Usos de 中</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>中 (zhōng) = en, durante, dentro de; indica algo en proceso (討論中). Leído zhòng significa «acertar, ganar» (中獎).</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>The Various Meanings of 中</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>中 (zhōng) means 'in / during', showing something is in progress (討論中). Read zhòng, it means 'to hit / win' (中獎).</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr">
+        <is>
+          <t>這個問題還在討論中。
+Este asunto todavía está en discusión.
+This issue is still under discussion.
+他中了大獎，高興得跳起來。
+Ganó el premio mayor y saltó de alegría.
+He won the jackpot and jumped for joy.</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>應徵</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>似乎 it seems that, it gives somebody the impression that</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>似乎</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>「似乎」表示根據看到或聽到的情況，覺得好像是這樣，語氣比「好像」稍微正式。</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Parece que: 似乎</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>似乎 = parece que. Expresa una impresión o suposición, con tono algo más formal que 好像.</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>似乎 it seems that, it gives somebody the impression that</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>似乎 means 'it seems that': an impression or guess based on what you see or hear, a bit more formal than 好像.</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>他似乎不太高興。
+Parece que no está muy contento.
+He doesn't seem very happy.
+天氣似乎快要變了。
+Parece que el clima está por cambiar.
+It looks like the weather is about to change.</t>
+        </is>
+      </c>
+      <c r="K329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>應徵</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>Classical Chinese Preposition 以</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>書面語介詞「以」</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>「以」是書面語的介詞，意思是「用、憑」，常見於「以……為……」「以電話」「以免」等。</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>«Con» formal: 以</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>以 es una preposición de lengua escrita: «con, por medio de». Se ve en 以…為…, 以電話, 以免.</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>Classical Chinese Preposition 以</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>以 is a written-language preposition meaning 'with / by means of', seen in 以…為…, 以電話, 以免.</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>請以電子郵件與我們聯絡。
+Por favor, contáctenos por correo electrónico.
+Please contact us by email.
+他以流利的中文介紹了自己。
+Se presentó en un chino fluido.
+He introduced himself in fluent Chinese.</t>
+        </is>
+      </c>
+      <c r="K330" s="2" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>應徵</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>是…的料 to be gifted in…</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>是……的料</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>「是……的料」表示天生適合做某件事，常用否定形式「不是……的料」。</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Tener madera: 是…的料</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>是…的料 = tener madera para, estar hecho para algo (un talento natural). Se usa más en la negación: 不是…的料.</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>是…的料 to be gifted in…</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>是…的料 means 'cut out for…': a natural talent for something, most often used negatively as 不是…的料.</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>他不是念書的料，可是很會畫畫。
+No tiene madera para estudiar, pero dibuja muy bien.
+He's not cut out for studying, but he draws very well.
+你天生就是當老師的料。
+Naciste para ser profesor.
+You were born to be a teacher.</t>
+        </is>
+      </c>
+      <c r="K331" s="2" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>應徵</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>Summary of 下去</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>「下去」的各種用法</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>動詞後面的「下去」可以表示往下走（走下去）、繼續做下去（做下去），否定時表示沒辦法再繼續（撐不下去）。</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Usos de 下去</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>下去 después de un verbo puede significar: ir hacia abajo (走下去), seguir haciendo algo (做下去) y, en negativo, no poder continuar (撐不下去).</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>Summary of 下去</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>下去 after a verb can mean going down (走下去), continuing (做下去), or, in the negative, being unable to carry on (撐不下去).</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>他從樓梯走下去了。
+Bajó por las escaleras.
+He went down the stairs.
+這個工作太累了，我做不下去了。
+Este trabajo es muy agotador; no puedo seguir con él.
+This job is too tiring; I can't keep doing it.</t>
+        </is>
+      </c>
+      <c r="K332" s="2" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>應徵</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>自 from (formal)</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>書面語「自」</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>「自」是書面語，意思是「從」，常見於「自古以來」「自……起」。</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>«Desde» formal: 自</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>自 = desde (lengua escrita o formal): 自古以來, 自…起. Equivale a 從 en un registro más formal.</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>自 from (formal)</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>自 is a formal, written word meaning 'from / since', as in 自古以來 and 自…起.</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr">
+        <is>
+          <t>這個習俗自古流傳至今。
+Esta costumbre se ha transmitido desde la antigüedad hasta hoy.
+This custom has been passed down from ancient times to the present.
+本店自五月一日起調整營業時間。
+A partir del 1 de mayo esta tienda cambia su horario.
+Starting May 1, this shop is changing its business hours.</t>
+        </is>
+      </c>
+      <c r="K333" s="2" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>4-11</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>文化、種族的大熔爐</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>偏偏 contrary to expectation, against the speaker’s wish, annoyingly</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>偏偏</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>「偏偏」表示事情剛好跟希望的相反，或故意跟別人的意見相反，常有一點不高興或無奈的語氣。</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Justo cuando: 偏偏</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>偏偏 = justo, precisamente (contra lo que se desea). Se usa para algo molesto o contrario a la voluntad de alguien.</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>偏偏 contrary to expectation, against the speaker’s wish, annoyingly</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>偏偏 means 'of all things / just when': things turn out contrary to what's wanted, or someone stubbornly does the opposite, often with an annoyed tone.</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr">
+        <is>
+          <t>我正要出門，偏偏下起雨來了。
+Justo cuando iba a salir, se puso a llover.
+Just as I was about to go out, it started raining.
+大家都說不要去，他偏偏要去。
+Todos dijeron que no fuera, pero él se empeñó en ir.
+Everyone told him not to go, but he insisted on going.</t>
+        </is>
+      </c>
+      <c r="K334" s="2" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>4-11</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>文化、種族的大熔爐</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>照 persist</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>照（照樣、照常）</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>「照」加動詞（照樣、照常）表示不管情況有沒有改變，還是照以前的方式做。</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Como siempre: 照</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>照 + verbo (照樣, 照常) = hacer lo mismo que antes, a pesar del cambio o del obstáculo.</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>照 persist</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>照 + verb (照樣, 照常) means to carry on as before regardless of changes or obstacles.</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr">
+        <is>
+          <t>下雨也照常上課。
+Aunque llueva, la clase se da como siempre.
+Class goes on as usual even when it rains.
+他被罵了，可是還是照樣遲到。
+Lo regañaron, pero igual llegó tarde como siempre.
+He got scolded, but he still showed up late as usual.</t>
+        </is>
+      </c>
+      <c r="K335" s="2" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>4-11</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>文化、種族的大熔爐</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>難得 rarely</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>難得</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>「難得」表示不常有、很少發生，所以特別可貴。也可以當形容詞，意思是「珍貴」。</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Raro: 難得</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>難得 = raro, poco frecuente; algo que no ocurre a menudo y por eso se valora. También es adjetivo: «valioso».</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>難得 rarely</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>難得 means 'rare / seldom': something that doesn't happen often and is therefore valued. It can also be an adjective meaning 'precious'.</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr">
+        <is>
+          <t>今天難得有空，我們出去走走吧。
+Hoy por fin tengo tiempo libre, salgamos a pasear.
+For once I have some free time today; let's go for a walk.
+這麼好的機會很難得，不要錯過。
+Una oportunidad así es poco común; no la dejes pasar.
+An opportunity this good is rare; don't miss it.</t>
+        </is>
+      </c>
+      <c r="K336" s="2" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>4-11</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>文化、種族的大熔爐</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>在…之餘 while not otherwise engaged in …, apart from…</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>在……之餘</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>「在……之餘」表示除了主要的事以外，在剩下的時間裡還做了別的事。</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>En ratos libres: 在…之餘</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>在…之餘 = además de / en los ratos libres de (una actividad principal), también se hace otra cosa.</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>在…之餘 while not otherwise engaged in …, apart from…</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>在…之餘 means 'in the time left over from (a main activity)': besides the main thing, you also did something else.</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr">
+        <is>
+          <t>在工作之餘，他學會了彈吉他。
+En sus ratos libres del trabajo, aprendió a tocar la guitarra.
+In his spare time from work, he learned to play the guitar.
+在忙碌之餘，也要記得多休息。
+Aun con mucho trabajo, recuerda descansar.
+Even when you're busy, remember to rest more.</t>
+        </is>
+      </c>
+      <c r="K337" s="2" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>4-11</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>文化、種族的大熔爐</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>難以 to find it difficult to…</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>難以</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>「難以」加動詞表示很難做到，語氣正式，常搭配雙音節動詞，例如「難以相信」「難以想像」。</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Difícil de: 難以</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>難以 + verbo = difícil de…. Es formal y se usa con verbos de dos sílabas: 難以相信, 難以想像.</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>難以 to find it difficult to…</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>難以 + verb means 'difficult to…'. It is formal and usually pairs with two-syllable verbs, as in 難以相信 and 難以想像.</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>這種感覺難以用言語形容。
+Este sentimiento es difícil de describir con palabras.
+This feeling is hard to put into words.
+他的話讓人難以相信。
+Sus palabras son difíciles de creer.
+His words are hard to believe.</t>
+        </is>
+      </c>
+      <c r="K338" s="2" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>4-11</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>文化、種族的大熔爐</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>漸漸 gradually, slowly</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>漸漸</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>「漸漸」表示變化慢慢地、一步一步地發生，意思是「慢慢地」。</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Poco a poco: 漸漸</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>漸漸 = poco a poco, gradualmente. Describe un cambio lento que va avanzando.</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>漸漸 gradually, slowly</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>漸漸 means 'gradually': a change happens slowly, step by step.</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr">
+        <is>
+          <t>天氣漸漸變冷了。
+El clima se está poniendo frío poco a poco.
+The weather is gradually getting colder.
+住久了，我漸漸習慣了這裡的生活。
+Con el tiempo me fui acostumbrando a la vida aquí.
+After living here a while, I gradually got used to life here.</t>
+        </is>
+      </c>
+      <c r="K339" s="2" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>4-11</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>文化、種族的大熔爐</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>可見 It can thus be concluded that…</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>可見</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>「可見」表示從前面的事實可以得到一個結論，意思是「由此可知」。</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Se ve que: 可見</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>可見 = se puede ver que, esto demuestra que. Saca una conclusión a partir de lo anterior.</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>可見 It can thus be concluded that…</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>可見 means 'it can be seen that': you draw a conclusion from the facts just mentioned.</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>他每天練習三個小時，可見他有多認真。
+Practica tres horas al día; eso demuestra lo aplicado que es.
+He practices three hours every day, which shows how dedicated he is.
+這家店天天大排長龍，可見很受歡迎。
+Esta tienda tiene fila larga todos los días; se ve que es muy popular.
+This shop has a long line every day, so clearly it's very popular.</t>
+        </is>
+      </c>
+      <c r="K340" s="2" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>4-11</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>文化、種族的大熔爐</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>對於…而言 as far as… is concerned</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>對於……而言</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>「對於 X 而言」表示從 X 的角度來看，是「對 X 來說」的比較正式說法。</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Para X: 對於…而言</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>對於 X 而言 = para X, en lo que se refiere a X. Es la forma más formal de 對 X 來說.</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>對於…而言 as far as… is concerned</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>對於 X 而言 means 'as far as X is concerned': a more formal version of 對 X 來說.</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>對於初學者而言，聲調是最難的部分。
+Para los principiantes, los tonos son la parte más difícil.
+For beginners, the tones are the hardest part.
+對於很多人而言，健康比賺錢更重要。
+Para mucha gente, la salud es más importante que ganar dinero.
+For many people, health is more important than making money.</t>
+        </is>
+      </c>
+      <c r="K341" s="2" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>4-12</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>期待美好的未來</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>無所謂 does not matter</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>無所謂</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>「無所謂」表示怎麼樣都可以，不在意，沒有特別的意見。</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Da igual: 無所謂</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>無所謂 = da igual, no importa. Se dice cuando a uno le es indiferente la opción.</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>無所謂 does not matter</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>無所謂 means 'it doesn't matter / I don't mind': you're indifferent to the choice.</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>吃什麼我都無所謂。
+Me da igual qué comer.
+I don't mind what we eat.
+對他來說，輸贏無所謂。
+Para él, ganar o perder no importa.
+For him, winning or losing doesn't matter.</t>
+        </is>
+      </c>
+      <c r="K342" s="2" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>4-12</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>期待美好的未來</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>誰知道 who would have thought…?</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>誰知道</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>「誰知道」表示出乎意料，常用在原本的計畫之後，意思是「沒想到」。也可以表示「不知道」。</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>¿Quién iba a decir?: 誰知道</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>誰知道 = ¿quién iba a pensar…? (algo inesperado después de lo planeado). También puede significar «quién sabe».</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>誰知道 who would have thought…?</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>誰知道 means 'who would have thought': something unexpected happens after the plan. It can also mean 'who knows'.</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>本來想去爬山，誰知道突然下起大雨。
+Pensábamos ir a la montaña, pero quién iba a decir que de repente llovería a cántaros.
+We meant to go hiking, but who would have thought it would suddenly pour.
+誰知道他到底在想什麼？
+¿Quién sabe qué estará pensando en realidad?
+Who knows what he's really thinking?</t>
+        </is>
+      </c>
+      <c r="K343" s="2" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>4-12</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>期待美好的未來</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>小自…大至… everything from A to Z</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>小自……大至……</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>「小自 A，大至 B」表示範圍很廣，從最小的 A 到最大的 B 都包括在內。</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>De A hasta B: 小自…大至…</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>小自 A，大至 B = desde A (lo más pequeño) hasta B (lo más grande): abarca todo el rango.</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>小自…大至… everything from A to Z</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>小自 A, 大至 B means 'from the smallest A to the biggest B': it covers the whole range.</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>小自一杯咖啡，大至一棟房子，網路上什麼都買得到。
+Desde un café hasta una casa, en internet se puede comprar de todo.
+From a cup of coffee to a house, you can buy anything online.
+小自個人生活，大至國家大事，他都有自己的看法。
+Desde la vida personal hasta los asuntos del país, tiene su propia opinión de todo.
+From personal life to affairs of state, he has his own opinion on everything.</t>
+        </is>
+      </c>
+      <c r="K344" s="2" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>4-12</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>期待美好的未來</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>竟然 to the speaker’s great surprise</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>竟然</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>「竟然」表示說話的人覺得很意外，沒想到事情會這樣。</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>¡Increíble!: 竟然</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>竟然 = ¡increíblemente!, ¡quién lo diría! Expresa gran sorpresa del hablante ante algo inesperado.</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>竟然 to the speaker’s great surprise</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>竟然 expresses the speaker's great surprise that something turned out unexpectedly.</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>他竟然沒有告訴我就搬家了。
+¡Increíble, se mudó sin decirme nada!
+Unbelievably, he moved without telling me.
+這麼簡單的題目，他竟然答錯了。
+Una pregunta tan fácil, ¡y la respondió mal!
+Such an easy question, and he got it wrong!</t>
+        </is>
+      </c>
+      <c r="K345" s="2" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>4-12</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>期待美好的未來</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>照理說 normally</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>照理說</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>「照理說」表示依照一般的道理，事情應該是這樣，後面常常接著說實際上不是這樣。</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>En teoría: 照理說</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>照理說 = en teoría, normalmente. Plantea lo que debería ser lo normal, y suele seguir un contraste.</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>照理說 normally</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>照理說 means 'normally / in theory': it states what should be the case, and is often followed by a contrast.</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>照理說，他應該已經到了。
+En teoría, ya debería haber llegado.
+In theory, he should have arrived by now.
+照理說這個時間不會塞車，可是今天卻塞得很嚴重。
+Normalmente a esta hora no hay tráfico, pero hoy hay mucho.
+Normally there's no traffic at this hour, but today it's really bad.</t>
+        </is>
+      </c>
+      <c r="K346" s="2" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>4-12</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>期待美好的未來</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>以A為B to take A as B</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>以 A 為 B</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>「以 A 為 B」表示把 A 當作 B，例如當作榜樣、重點或基礎，語氣正式。</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Tomar A como B: 以A為B</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>以 A 為 B = tomar A como B (como modelo, prioridad o base). Es formal.</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>以A為B to take A as B</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>以 A 為 B means 'take A as B': as a model, priority or basis. It is formal.</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>這間公司以客戶為第一。
+Esta empresa pone al cliente en primer lugar.
+This company puts customers first.
+他以老師為榜樣，努力學習。
+Toma a su profesor como modelo y estudia con esfuerzo.
+He takes his teacher as a role model and studies hard.</t>
+        </is>
+      </c>
+      <c r="K347" s="2" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>4-12</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>期待美好的未來</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>無論…都… regardless of what…</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>無論……都……</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>「無論……都……」表示不管是哪一種情況，結果都一樣。「無論」後面通常有疑問詞或選擇。</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>No importa…: 無論…都…</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>無論…都… = no importa qué / cómo…, siempre…. Introduce una condición con varias opciones y el mismo resultado.</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>無論…都… regardless of what…</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>無論…都… means 'no matter what/how…, always…': the result is the same in every case. 無論 is usually followed by a question word or choices.</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>無論天氣好不好，他都會去跑步。
+Haga buen tiempo o no, él siempre sale a correr.
+Whether the weather is good or not, he goes running.
+無論你說什麼，我都不會改變主意。
+Digas lo que digas, no voy a cambiar de opinión.
+No matter what you say, I won't change my mind.</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>4-12</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>期待美好的未來</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>明明 It should be obvious to everyone that…</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>明明</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>「明明」表示事實很清楚，可是說的話或做的事卻和事實不一樣，常有責怪或不滿的語氣。</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Claramente: 明明</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>明明 = claramente, a todas luces. Se usa cuando algo es obvio pero lo que se dice o hace lo contradice.</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>明明 It should be obvious to everyone that…</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>明明 means 'obviously': the facts are clear, yet what is said or done contradicts them, often with a tone of blame or dissatisfaction.</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>明明是你自己說要去的，現在怎麼又不去了？
+Fuiste tú mismo quien dijo que iría, ¿cómo es que ahora no vas?
+You were the one who said you'd go; why aren't you going now?
+他明明知道答案，卻假裝不知道。
+Claramente sabe la respuesta, pero finge que no.
+He obviously knows the answer, but he pretends not to.</t>
+        </is>
+      </c>
+      <c r="K349" s="2" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>4-12</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>期待美好的未來</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>Causation with 使得</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>使得</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>「使得」表示某件事造成了某個結果，主語常常不是人。</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Hacer que: 使得</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>使得 = hacer que, provocar. Expresa que un hecho causa un resultado (suele ser un sujeto no humano).</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>Causation with 使得</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>使得 means 'to cause / make': one event causes a result, and the subject is often not a person.</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>這場大雨使得很多航班取消了。
+Esta fuerte lluvia hizo que se cancelaran muchos vuelos.
+This heavy rain caused many flights to be canceled.
+網路的發展使得生活更方便。
+El desarrollo de internet hizo la vida más cómoda.
+The development of the internet has made life more convenient.</t>
+        </is>
+      </c>
+      <c r="K350" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
